--- a/selenium_model/UNIT_TESTING_350_REPORT.xlsx
+++ b/selenium_model/UNIT_TESTING_350_REPORT.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F211" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F212" t="n">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F298" t="n">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F350" t="n">
